--- a/data/number_of_national_health_insurers/0096.xlsx
+++ b/data/number_of_national_health_insurers/0096.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ivpf201v.takamatsu.local\Profile\t10339\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\userdata\m7812\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D816B6-D720-489C-9BC6-BA7F23356D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="804" windowWidth="22140" windowHeight="12180"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>#property</t>
   </si>
@@ -102,13 +103,21 @@
   </si>
   <si>
     <t>2024.3.31</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高松市</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2025.3.31</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -488,8 +497,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -634,6 +643,20 @@
       </c>
       <c r="D9" s="1">
         <v>68290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="1">
+        <v>65073</v>
       </c>
     </row>
   </sheetData>
